--- a/artfynd/A 26766-2026 artfynd.xlsx
+++ b/artfynd/A 26766-2026 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104154718</v>
+        <v>119820241</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Myrheden, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739043.5604490344</v>
+        <v>739242</v>
       </c>
       <c r="R2" t="n">
-        <v>7318837.710462634</v>
+        <v>7318761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820245</v>
+        <v>119820247</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739411</v>
+        <v>739467</v>
       </c>
       <c r="R3" t="n">
-        <v>7318716</v>
+        <v>7318715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820249</v>
+        <v>119820243</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,14 +922,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vitberget, Nb</t>
+          <t>Myrheden, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739432</v>
+        <v>739277</v>
       </c>
       <c r="R4" t="n">
-        <v>7318698</v>
+        <v>7318737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820244</v>
+        <v>119820249</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,14 +1028,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrheden, Nb</t>
+          <t>Vitberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739326</v>
+        <v>739432</v>
       </c>
       <c r="R5" t="n">
-        <v>7318719</v>
+        <v>7318698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820241</v>
+        <v>119820245</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,14 +1134,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myrheden, Nb</t>
+          <t>Vitberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739242</v>
+        <v>739411</v>
       </c>
       <c r="R6" t="n">
-        <v>7318761</v>
+        <v>7318716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820250</v>
+        <v>119820244</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,14 +1240,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitberget, Nb</t>
+          <t>Myrheden, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739432</v>
+        <v>739326</v>
       </c>
       <c r="R7" t="n">
-        <v>7318698</v>
+        <v>7318719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820243</v>
+        <v>119820248</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,14 +1346,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Myrheden, Nb</t>
+          <t>Vitberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739277</v>
+        <v>739432</v>
       </c>
       <c r="R8" t="n">
-        <v>7318737</v>
+        <v>7318699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119820247</v>
+        <v>119820250</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1502,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739467</v>
+        <v>739432</v>
       </c>
       <c r="R9" t="n">
-        <v>7318715</v>
+        <v>7318698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119820248</v>
+        <v>104154718</v>
       </c>
       <c r="B10" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,38 +1534,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitberget, Nb</t>
+          <t>Myrheden, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739432</v>
+        <v>739044</v>
       </c>
       <c r="R10" t="n">
-        <v>7318699</v>
+        <v>7318838</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,17 +1588,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26766-2026 artfynd.xlsx
+++ b/artfynd/A 26766-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820247</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820244</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820248</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820250</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,8 +1667,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154718</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>